--- a/data_extactor/batch_10_fa/trimmed/batch_0002_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0002_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | ایمنی و امنیت عمومی | امور اداری و منابع انسانی | مکانیک | ساختمان و ساخت‌وساز | مهندسی و فناوری</t>
+          <t>مدیریت و اداره | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مکانیک | ساختمان و ساخت‌وساز | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران ساخت‌وساز | بازرسان ساختمان و سازه | سرپرستان رده‌اول مکانیک‌ها، نصاب‌ها و تعمیرکاران | کارگران عمومی نگهداری و تعمیرات | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مدیران حراست و انتظامات</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | کارگران عمومی تعمیرات و نگهداری تاسیسات | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت | سخن گفتن | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | سخن گفتن | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | مدیریت و امور اداری | امور اداری و منابع انسانی | آموزش و تدریس | رایانه و الکترونیک | مخابرات</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | مدیریت و اداره | پرسنل و منابع انسانی | آموزش و پرورش | رایانه و الکترونیک | مخابرات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران مدیریت بحران | سرپرستان رده‌اول مأموران حراست و نگهبانی | مأموران نظارت تصویری و بازرسان اماکن ویژه | کارشناسان امنیت اطلاعات | نگهبانان و مأموران حفاظت | متخصصان مدیریت حراست و امنیت</t>
+          <t>مدیران مدیریت بحران و پدافند غیرعامل | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | تحلیل‌گران امنیت اطلاعات | نگهبانان و ماموران حراست | کارشناسان مدیریت حراست و امنیت فیزیکی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | مهندسی و فناوری | زبان انگلیسی | امور اداری و منابع انسانی | ریاضیات</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | پرسنل و منابع انسانی | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | مدیران پایگاه داده | کارشناسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | راهبران شبکه و سیستم‌های رایانه‌ای | توسعه‌دهندگان نرم‌افزار</t>
+          <t>معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | اقتصاد و حسابداری | ریاضیات | اداری | حقوق و مقررات دولتی | امور اداری و منابع انسانی</t>
+          <t>مدیریت و اداره | اقتصاد و حسابداری | ریاضیات | اداری | قانون و دولت | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | مهارت محاسبات عددی | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیل‌گران بودجه | تحلیل‌گران اعتباری | ممیزان و بازرسان مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | خزانه‌داران و مدیران مالی</t>
+          <t>حسابداران و حسابرسان | تحلیل‌گران بودجه | تحلیل‌گران اعتبارات و تسهیلات | بازرسان و ارزیابان مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | امور اداری و منابع انسانی</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | مدیریت و اداره | ریاضیات | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیل‌گران بودجه | ممیزان و بازرسان مالی | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | تحلیل‌گران مدیریت</t>
+          <t>حسابداران و حسابرسان | تحلیل‌گران بودجه | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | حقوق و مقررات دولتی | رایانه و الکترونیک</t>
+          <t>اقتصاد و حسابداری | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی | مهارت محاسبات عددی</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | توانایی عددی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیل‌گران اعتباری | اقتصاددانان | مدیران امور مالی | تحلیل‌گران کمی مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی</t>
+          <t>حسابداران و حسابرسان | تحلیل‌گران اعتبارات و تسهیلات | اقتصاددانان | مدیران امور مالی | تحلیل‌گران کمّی مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | استراتژی‌های یادگیری | یادگیری فعال | نگارش | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مدیریت و امور اداری | ریاضیات | امور اداری و منابع انسانی | مکانیک | مهندسی و فناوری</t>
+          <t>تولید و فرآوری | مدیریت و اداره | ریاضیات | پرسنل و منابع انسانی | مکانیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیاتی | مهندسان صنایع | مهندسان ساخت و تولید | مدیران سیستم‌های کنترل کیفیت | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>سرپرستان رده اول کارگران تولید و عملیات | مدیران کل و مدیران عملیات | مهندسان صنایع | مهندسان تولید و ساخت | مدیران سیستم‌های کنترل کیفیت | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | شیمی | مدیریت و امور اداری | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
+          <t>تولید و فرآوری | شیمی | مدیریت و اداره | ریاضیات | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های فنی کالیبراسیون | مدیران انطباق و نظارت بر مقررات | مهندسان صنایع | مدیران تولید صنعتی | بازرسان، آزمایشگران، درجه‌بندان، نمونه‌برداران و توزین‌گران | تحلیل‌گران کنترل کیفیت | مهندسان اعتبارسنجی و صحه‌گذاری فرایند</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مدیران تطبیق و نظارت مقرراتی | مهندسان صنایع | مدیران تولید صنعتی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان تحلیل کنترل کیفیت | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | شنیدن فعال | نگارش | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | مدیریت و امور اداری | تولید و فراوری | ایمنی و امنیت عمومی | مهندسی و فناوری | امور اداری و منابع انسانی | فیزیک</t>
+          <t>مکانیک | مدیریت و اداره | تولید و فرآوری | ایمنی و امنیت عمومی | مهندسی و فناوری | پرسنل و منابع انسانی | فیزیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان انرژی، به‌جز باد و خورشید | اپراتورهای تأسیسات و پالایشگاه گاز | تکنسین‌های انرژی زمین‌گرمایی | مدیران نیروگاه‌های برق‌آبی | مدیران تولید صنعتی | اپراتورهای نیروگاه | مدیران سیستم‌های کنترل کیفیت</t>
+          <t>مهندسان انرژی، به‌جز بادی و خورشیدی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های سامانه‌های زمین‌گرمایی | مدیران تولید نیروگاه‌های برق‌آبی | مدیران تولید صنعتی | اپراتورهای نیروگاه برق | مدیران سیستم‌های کنترل کیفیت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نظارت | سخن گفتن | نگارش | استراتژی‌های یادگیری | یادگیری فعال | علوم پایه | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | نگارش | راهبردهای یادگیری | یادگیری فعال | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مدیریت و امور اداری | مکانیک | مهندسی و فناوری | شیمی | ریاضیات | امور اداری و منابع انسانی</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک | مهندسی و فناوری | شیمی | ریاضیات | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران توسعه فناوری و محصولات سوخت زیستی | مهندسان شیمی | اپراتورهای فرایند و کارخانه‌های شیمیایی | مهندسان صنایع | مدیران تولید صنعتی | مدیران سیستم‌های کنترل کیفیت</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | مهندسان صنایع | مدیران تولید صنعتی | مدیران سیستم‌های کنترل کیفیت</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
